--- a/Treinamento/GeraBlocoBCadastroCorretor.xlsx
+++ b/Treinamento/GeraBlocoBCadastroCorretor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECCEE9B-973F-401E-AFD1-E4F246B3D5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A48CF9AA-5CB9-41E4-96D4-01B05ACF9749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -488,7 +488,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
-        <v>4036291</v>
+        <v>4036332</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>5</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
-        <v>4036293</v>
+        <v>4036350</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>5</v>
@@ -510,7 +510,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
-        <v>4036299</v>
+        <v>4036331</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>5</v>
@@ -520,7 +520,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
-        <v>4036303</v>
+        <v>4036345</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>5</v>
@@ -529,7 +529,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
-        <v>4036294</v>
+        <v>4036330</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>5</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
-        <v>4036302</v>
+        <v>4036325</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>5</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
-        <v>4036304</v>
+        <v>4036337</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>5</v>
@@ -556,7 +556,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
-        <v>4036301</v>
+        <v>4036335</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>5</v>
@@ -566,7 +566,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
-        <v>4036300</v>
+        <v>4036327</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>5</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
-        <v>4036289</v>
+        <v>4036328</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>5</v>
@@ -588,7 +588,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
-        <v>4036297</v>
+        <v>4036329</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>5</v>
@@ -597,7 +597,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
-        <v>4036298</v>
+        <v>4036339</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>5</v>
@@ -606,7 +606,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
-        <v>4036290</v>
+        <v>4036344</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>5</v>
@@ -615,7 +615,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>4036292</v>
+        <v>4036343</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>5</v>
@@ -623,7 +623,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>4036296</v>
+        <v>4036354</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>5</v>
@@ -631,7 +631,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>4036295</v>
+        <v>4036336</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>5</v>
@@ -639,7 +639,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>4036316</v>
+        <v>4036353</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>5</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>4036319</v>
+        <v>4036352</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>5</v>
@@ -655,7 +655,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>4036313</v>
+        <v>4036341</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>5</v>
@@ -663,7 +663,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>4036314</v>
+        <v>4036333</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>5</v>
@@ -671,7 +671,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>4036310</v>
+        <v>4036334</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>5</v>
@@ -679,7 +679,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>4036318</v>
+        <v>4036338</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>5</v>
@@ -687,7 +687,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>4036311</v>
+        <v>4036340</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>5</v>
@@ -695,7 +695,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>4036315</v>
+        <v>4036342</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>5</v>
@@ -703,7 +703,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>4036312</v>
+        <v>4036346</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>5</v>
@@ -711,7 +711,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>4036317</v>
+        <v>4036351</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>5</v>
@@ -731,31 +731,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GeraBlocoBCadastroCorretor.xlsx
+++ b/Treinamento/GeraBlocoBCadastroCorretor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0DA725-4E1C-4B25-8379-585C714DDCF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7A095D-2DB1-4316-8B45-769DCCACC2B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="6">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -462,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="4" customWidth="1" collapsed="1"/>
@@ -487,9 +487,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>4036455</v>
-      </c>
+      <c r="A2" s="7"/>
       <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
@@ -497,9 +495,7 @@
       <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <v>4036427</v>
-      </c>
+      <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
@@ -509,9 +505,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>4036458</v>
-      </c>
+      <c r="A4" s="7"/>
       <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
@@ -519,45 +513,35 @@
       <c r="D4" s="6"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>4036428</v>
-      </c>
+      <c r="A5" s="7"/>
       <c r="B5" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="6"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>4036462</v>
-      </c>
+      <c r="A6" s="7"/>
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="6"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>4036446</v>
-      </c>
+      <c r="A7" s="8"/>
       <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="6"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>4036456</v>
-      </c>
+      <c r="A8" s="7"/>
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="6"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>4036459</v>
-      </c>
+      <c r="A9" s="7"/>
       <c r="B9" s="5" t="s">
         <v>5</v>
       </c>
@@ -565,9 +549,7 @@
       <c r="D9" s="6"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>4036432</v>
-      </c>
+      <c r="A10" s="7"/>
       <c r="B10" s="5" t="s">
         <v>5</v>
       </c>
@@ -577,9 +559,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>4036423</v>
-      </c>
+      <c r="A11" s="7"/>
       <c r="B11" s="5" t="s">
         <v>5</v>
       </c>
@@ -587,191 +567,25 @@
       <c r="D11" s="6"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>4036424</v>
-      </c>
+      <c r="A12" s="7"/>
       <c r="B12" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>4036437</v>
-      </c>
+      <c r="A13" s="7"/>
       <c r="B13" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="6"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>4036447</v>
-      </c>
+      <c r="A14" s="7"/>
       <c r="B14" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="6"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>4036422</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>4036457</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>4036445</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>4036426</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>4036461</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <v>4036433</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <v>4036454</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <v>4036438</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <v>4036434</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
-        <v>4036435</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <v>4036436</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
-        <v>4036442</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
-        <v>4036444</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
-        <v>4036443</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
-        <v>4036441</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
-        <v>4036440</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
-        <v>4036439</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
-        <v>4036431</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
-        <v>4036430</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
-        <v>4036460</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -787,31 +601,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>